--- a/data/trans_orig/Q5418_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5418_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de lavarse la ropa en 2023</t>
+          <t>Población según si es capaz de lavarse la ropa en 2023 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30148</t>
+          <t>30503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47959</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67474</t>
+          <t>66722</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91084</t>
+          <t>90161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99659</t>
+          <t>102503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>130363</t>
+          <t>131476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22753</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39099</t>
+          <t>39476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55533</t>
+          <t>54683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75585</t>
+          <t>76132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81916</t>
+          <t>81061</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108324</t>
+          <t>109256</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>185690</t>
+          <t>185313</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>209131</t>
+          <t>207665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>342768</t>
+          <t>342775</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>370697</t>
+          <t>372939</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>537443</t>
+          <t>537133</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>574130</t>
+          <t>575309</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,04%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17717</t>
+          <t>16859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23838</t>
+          <t>23359</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37851</t>
+          <t>37370</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53569</t>
+          <t>52768</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>237941</t>
+          <t>238081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>253132</t>
+          <t>253396</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>402254</t>
+          <t>403284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>446754</t>
+          <t>447345</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>649579</t>
+          <t>649225</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>706919</t>
+          <t>706023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93864</t>
+          <t>93381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102192</t>
+          <t>102248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60453</t>
+          <t>60636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67672</t>
+          <t>67543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157040</t>
+          <t>156885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168187</t>
+          <t>168234</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40990</t>
+          <t>41814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>62434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45950</t>
+          <t>44032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112420</t>
+          <t>113154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90535</t>
+          <t>88786</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162182</t>
+          <t>162070</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39383</t>
+          <t>39680</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60798</t>
+          <t>62024</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>46190</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116748</t>
+          <t>118826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94969</t>
+          <t>88804</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>167061</t>
+          <t>166254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>528765</t>
+          <t>527956</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558073</t>
+          <t>557221</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>802533</t>
+          <t>800023</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933572</t>
+          <t>937001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1348111</t>
+          <t>1348847</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1484440</t>
+          <t>1494066</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5418_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5418_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38502</t>
+          <t>39633</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30503</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48013</t>
+          <t>49526</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>77046</t>
+          <t>82740</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66722</t>
+          <t>69292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90161</t>
+          <t>94981</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>115548</t>
+          <t>122373</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102503</t>
+          <t>108008</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131476</t>
+          <t>140960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30251</t>
+          <t>32882</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23731</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39476</t>
+          <t>42520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64864</t>
+          <t>70114</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54683</t>
+          <t>59196</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76132</t>
+          <t>81832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>95115</t>
+          <t>102996</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81061</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109256</t>
+          <t>119863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>197791</t>
+          <t>214637</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>185313</t>
+          <t>203616</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>207665</t>
+          <t>227318</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>358230</t>
+          <t>385281</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>342775</t>
+          <t>370405</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>372939</t>
+          <t>401699</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>556022</t>
+          <t>599918</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>537133</t>
+          <t>579000</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>575309</t>
+          <t>620077</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,13%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>266544</t>
+          <t>287152</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>266544</t>
+          <t>287152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>266544</t>
+          <t>287152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>500140</t>
+          <t>538135</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>500140</t>
+          <t>538135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500140</t>
+          <t>538135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>766685</t>
+          <t>825287</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>766685</t>
+          <t>825287</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>766685</t>
+          <t>825287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10164</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>17644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>18353</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>28547</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16486</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23359</t>
+          <t>25042</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>15664</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37370</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>35113</t>
+          <t>39073</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>30892</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52768</t>
+          <t>50103</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>246607</t>
+          <t>275491</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>238081</t>
+          <t>266139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>253396</t>
+          <t>282283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>428923</t>
+          <t>246376</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>403284</t>
+          <t>237557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>447345</t>
+          <t>253378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>675530</t>
+          <t>521867</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>649225</t>
+          <t>510677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>706023</t>
+          <t>532320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>682</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>99490</t>
+          <t>112544</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93381</t>
+          <t>106058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102248</t>
+          <t>115642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>64542</t>
+          <t>75292</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60636</t>
+          <t>70724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67543</t>
+          <t>78540</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>164030</t>
+          <t>187836</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156885</t>
+          <t>181294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168234</t>
+          <t>192906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104403</t>
+          <t>118292</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104403</t>
+          <t>118292</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104403</t>
+          <t>118292</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>175727</t>
+          <t>201147</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>175727</t>
+          <t>201147</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>175727</t>
+          <t>201147</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>50636</t>
+          <t>52701</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41814</t>
+          <t>42375</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62434</t>
+          <t>64128</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>85395</t>
+          <t>93446</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44032</t>
+          <t>79074</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113154</t>
+          <t>107243</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>136031</t>
+          <t>146147</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88786</t>
+          <t>128770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162070</t>
+          <t>164864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -2206,27 +2206,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49681</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>42966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62024</t>
+          <t>68301</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>90114</t>
+          <t>98240</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46190</t>
+          <t>85205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118826</t>
+          <t>112439</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>139795</t>
+          <t>152137</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88804</t>
+          <t>135376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>166254</t>
+          <t>171123</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>543887</t>
+          <t>602672</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>527956</t>
+          <t>585986</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>557221</t>
+          <t>618031</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>851695</t>
+          <t>706950</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>800023</t>
+          <t>689652</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>937001</t>
+          <t>726419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1395582</t>
+          <t>1309621</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1348847</t>
+          <t>1283103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1494066</t>
+          <t>1332283</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>644204</t>
+          <t>709269</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>644204</t>
+          <t>709269</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>644204</t>
+          <t>709269</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1027204</t>
+          <t>898636</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1027204</t>
+          <t>898636</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1027204</t>
+          <t>898636</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1671408</t>
+          <t>1607905</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1671408</t>
+          <t>1607905</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1671408</t>
+          <t>1607905</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
